--- a/generated_payslips.xlsx
+++ b/generated_payslips.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Desktop\payslip_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{146B9BB6-6410-499E-8D2B-26DD5413B2A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E70B853-DF1A-4886-A384-F0DF9FE84F5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{9D93CBE0-DAA0-4EF6-8845-43AC577E8CAD}"/>
+    <workbookView minimized="1" xWindow="5115" yWindow="2070" windowWidth="15375" windowHeight="7785" xr2:uid="{9D93CBE0-DAA0-4EF6-8845-43AC577E8CAD}"/>
   </bookViews>
   <sheets>
     <sheet name="New Hires" sheetId="4" r:id="rId1"/>
@@ -1515,37 +1515,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
